--- a/outputs_xlsx_solution/test_1.4-wide.xlsx
+++ b/outputs_xlsx_solution/test_1.4-wide.xlsx
@@ -77,7 +77,10 @@
     <t>fmul F8, F2, F3</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
   </si>
   <si>
     <t>fsub F9, F6, F3</t>
@@ -92,10 +95,10 @@
     <t>fsd F7, 128(X0)</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fsd F8, 132(X0)</t>
@@ -107,6 +110,9 @@
     <t>fsd F10, 140(X0)</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>[Legend]</t>
   </si>
   <si>
@@ -116,13 +122,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -531,12 +555,6 @@
       <c r="Q1">
         <v>14</v>
       </c>
-      <c r="R1">
-        <v>15</v>
-      </c>
-      <c r="S1">
-        <v>16</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -558,7 +576,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -581,10 +599,10 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -603,14 +621,17 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -629,14 +650,17 @@
       <c r="E5" t="s">
         <v>9</v>
       </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -655,14 +679,17 @@
       <c r="F6" t="s">
         <v>9</v>
       </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
       <c r="I6" t="s">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -685,13 +712,13 @@
         <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -711,19 +738,19 @@
         <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -746,16 +773,16 @@
         <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -766,7 +793,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -775,19 +802,19 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +825,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -810,28 +837,22 @@
         <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -842,7 +863,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -851,16 +872,16 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" t="s">
         <v>20</v>
       </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" t="s">
-        <v>19</v>
+      <c r="P12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +892,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -880,16 +901,16 @@
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" t="s">
         <v>20</v>
       </c>
-      <c r="N13" t="s">
-        <v>19</v>
-      </c>
-      <c r="R13" t="s">
-        <v>19</v>
+      <c r="P13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -900,7 +921,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -908,17 +929,23 @@
       <c r="H14" t="s">
         <v>9</v>
       </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
       <c r="M14" t="s">
         <v>14</v>
       </c>
       <c r="N14" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" t="s">
         <v>20</v>
       </c>
-      <c r="O14" t="s">
-        <v>19</v>
-      </c>
-      <c r="R14" t="s">
-        <v>19</v>
+      <c r="P14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +956,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -937,17 +964,20 @@
       <c r="H15" t="s">
         <v>9</v>
       </c>
+      <c r="M15" t="s">
+        <v>15</v>
+      </c>
       <c r="N15" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" t="s">
         <v>20</v>
       </c>
-      <c r="P15" t="s">
-        <v>19</v>
-      </c>
-      <c r="R15" t="s">
-        <v>19</v>
+      <c r="Q15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -958,7 +988,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -966,19 +996,22 @@
       <c r="H16" t="s">
         <v>9</v>
       </c>
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
       <c r="O16" t="s">
-        <v>14</v>
-      </c>
-      <c r="R16" t="s">
-        <v>20</v>
-      </c>
-      <c r="S16" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="P16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -986,7 +1019,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -994,31 +1027,55 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_1.4-wide.xlsx
+++ b/outputs_xlsx_solution/test_1.4-wide.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -147,6 +150,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -576,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -596,13 +602,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -622,16 +628,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -651,16 +657,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -680,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +724,7 @@
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -738,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -750,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +788,7 @@
         <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -793,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -802,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -814,7 +820,7 @@
         <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -825,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -852,7 +858,7 @@
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -863,7 +869,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -872,16 +878,16 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
         <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -892,7 +898,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -901,16 +907,16 @@
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
         <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -921,7 +927,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -930,22 +936,22 @@
         <v>9</v>
       </c>
       <c r="K14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" t="s">
         <v>15</v>
       </c>
-      <c r="L14" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" t="s">
-        <v>14</v>
-      </c>
       <c r="N14" t="s">
         <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -956,7 +962,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -965,19 +971,19 @@
         <v>9</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
         <v>14</v>
       </c>
       <c r="P15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -988,7 +994,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -997,21 +1003,21 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" t="s">
         <v>14</v>
       </c>
       <c r="Q16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1019,7 +1025,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1027,15 +1033,15 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1043,39 +1049,55 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
         <v>36</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
         <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
